--- a/Luban/Config/Datas/Levels/L22/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L22/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L22 W1/25; N=52; EHP=334.048000; normal:17x26,normal:18x26</t>
+          <t>L22 W1/25; N=52; EHP=883.499348; normal:17x26,normal:18x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L22 W2/25; N=58; EHP=390.141083; normal:17x29,normal:18x29</t>
+          <t>L22 W2/25; N=58; EHP=1031.855879; normal:17x29,normal:18x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10018901,10018903,10048731,10018901,10018903,10048731,10018901,10018903,10048732,10018901,10018903,10048733,10018901,10018903,10048733,10018901,10018903,10048734,10018901,10018903,10048734,10018901,10018903,10048735,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018901,10018901,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902</t>
+          <t>10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018903,10018901,10018901,10018901,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018902,10018901,10018901,10018901,10018901,10018901,10018901,10018901,10018901</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L22 W3/25; N=64; EHP=476.259942; air:2x2,air:11x1,air:12x2,air:13x2,air:14x1,normal:17x20,normal:18x19,swarm:84x17</t>
+          <t>L22 W3/25; N=64; EHP=1362.931128; normal:17x28,normal:18x19,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10018904,10018906,10048736,10018904,10018906,10048736,10018904,10018906,10048737,10018904,10018906,10048737,10018904,10018906,10048738,10018904,10018906,10048739,10018904,10018906,10048739,10018904,10018906,10048740,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018904,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905</t>
+          <t>10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018906,10018904,10018904,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905,10018905</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L22 W4/25; N=70; EHP=599.828152; air:2x2,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x21,normal:18x22,swarm:84x19</t>
+          <t>L22 W4/25; N=70; EHP=1704.853291; normal:17x21,normal:18x30,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10018907,10018910,10048741,10018909,10018907,10018910,10048742,10018909,10018907,10018910,10048742,10018909,10018907,10018910,10048743,10018909,10018907,10018910,10048743,10018911,10018907,10018910,10048744,10018911,10018907,10018910,10048744,10018911,10018907,10018910,10048745,10018912,10018907,10018910,10048745,10018912,10018907,10018910,10018912,10018907,10018910,10018912,10018907,10018910,10018907,10018910,10018907,10018910,10018907,10018910,10018907,10018910,10018907,10018910,10018907,10018910,10018908,10018910,10018908,10018910,10018908,10018910,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908</t>
+          <t>10018907,10048741,10048741,10018909,10018907,10048742,10048742,10018909,10018907,10048742,10048742,10018909,10018907,10048743,10048743,10018909,10018907,10048743,10048743,10018911,10018907,10048744,10048744,10018911,10018907,10048744,10048744,10018911,10018907,10048745,10048745,10018912,10018907,10048745,10048745,10018912,10018907,10018910,10018912,10018907,10018910,10018912,10018907,10018910,10018907,10018910,10018907,10018910,10018907,10018910,10018907,10018910,10018907,10018910,10018907,10018910,10018908,10018910,10018908,10018910,10018908,10018910,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908,10018908</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L22 W5/25; N=76; EHP=1122.000000; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x17,medium:83x4,swarm:84x21,medium:108x3,medium:123x4</t>
+          <t>L22 W5/25; N=76; EHP=3004.901912; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x3,medium:123x4,normal:17x18,normal:18x17,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10018916,10018922,10018918,10048746,10018921,10018916,10018922,10018918,10048746,10018921,10018916,10018922,10018918,10018913,10018921,10018916,10018922,10018919,10018913,10018921,10018916,10018922,10018919,10048747,10018924,10018916,10018922,10018920,10048747,10018924,10018916,10018922,10018920,10018914,10018924,10018916,10018922,10018923,10018914,10018924,10018916,10018922,10018923,10018915,10018925,10018916,10018922,10018915,10018925,10018916,10018922,10018925,10018916,10018922,10018925,10018916,10018922,10018916,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018917,10018917,10018917,10018917,10018917,10018917</t>
+          <t>10018916,10048746,10018918,10048746,10018921,10018916,10048746,10018918,10048746,10018921,10018916,10018913,10018918,10018913,10018921,10018916,10018913,10018919,10018913,10018921,10018916,10048747,10018919,10048747,10018924,10018916,10048747,10018920,10048747,10018924,10018916,10018914,10018920,10018914,10018924,10018916,10018914,10018923,10018914,10018924,10018916,10018915,10018923,10018915,10018925,10018916,10018915,10018915,10018925,10018916,10018922,10018925,10018916,10018922,10018925,10018916,10018922,10018916,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018922,10018917,10018917,10018917,10018917,10018917,10018917,10018917</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L22 W6/25; N=82; EHP=1145.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x15,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x22,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L22 W6/25; N=82; EHP=3068.252742; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x15,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10018929,10018935,10018931,10048748,10018934,10018929,10018935,10018931,10048748,10018934,10018929,10018935,10018932,10018926,10018934,10018929,10018935,10018932,10018926,10018934,10018929,10018935,10018932,10048749,10018937,10018929,10018935,10018933,10048749,10018937,10018929,10018935,10018933,10018927,10018937,10018929,10018935,10018936,10018927,10018937,10018929,10018935,10018936,10018928,10018937,10018929,10018935,10018936,10018928,10018938,10018929,10018935,10018928,10018938,10018929,10018935,10018938,10018929,10018935,10018938,10018929,10018935,10018929,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018930,10018930,10018930,10018930,10018930</t>
+          <t>10018929,10048748,10018931,10048748,10018934,10018929,10048748,10018931,10048748,10018934,10018929,10018926,10018932,10018926,10018934,10018929,10018926,10018932,10018926,10018934,10018929,10048749,10018932,10048749,10018937,10018929,10048749,10018933,10048749,10018937,10018929,10018927,10018933,10018927,10018937,10018929,10018927,10018936,10018927,10018937,10018929,10018928,10018936,10018928,10018937,10018929,10018928,10018936,10018928,10018938,10018929,10018928,10018928,10018938,10018929,10018935,10018938,10018929,10018935,10018938,10018929,10018935,10018929,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018935,10018930,10018930,10018930,10018930,10018930,10018930</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L22 W7/25; N=88; EHP=1284.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x3,normal:17x15,normal:18x15,fast:30x2,fast:58x3,fast:64x2,medium:83x4,swarm:84x24,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L22 W7/25; N=88; EHP=3441.991265; air:2x4,air:11x4,air:12x4,air:13x4,air:14x6,fast:30x2,fast:58x3,fast:64x2,fast:98x3,medium:83x4,medium:108x5,medium:123x4,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10018942,10018948,10018944,10048750,10018947,10018942,10018948,10018944,10048750,10018947,10018942,10018948,10018944,10018939,10018947,10018942,10018948,10018945,10018939,10018947,10018942,10018948,10018945,10048751,10018947,10018942,10018948,10018945,10048751,10018950,10018942,10018948,10018946,10048751,10018950,10018942,10018948,10018946,10018940,10018950,10018942,10018948,10018946,10018940,10018950,10018942,10018948,10018949,10018941,10018951,10018942,10018948,10018949,10018941,10018951,10018942,10018948,10018951,10018942,10018948,10018951,10018942,10018948,10018951,10018942,10018948,10018942,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018943,10018943,10018943,10018943,10018943</t>
+          <t>10018942,10048750,10018944,10048750,10018947,10018942,10048750,10018944,10048750,10018947,10018942,10018939,10018944,10018939,10018947,10018942,10018939,10018945,10018939,10018947,10018942,10048751,10018945,10048751,10018947,10018942,10048751,10018945,10048751,10018950,10018942,10048751,10018946,10048751,10018950,10018942,10018940,10018946,10018940,10018950,10018942,10018940,10018946,10018940,10018950,10018942,10018941,10018949,10018941,10018951,10018942,10018941,10018949,10018941,10018951,10018942,10018948,10018951,10018942,10018948,10018951,10018942,10018948,10018951,10018942,10018948,10018942,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018948,10018943,10018943,10018943,10018943,10018943,10018943</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L22 W8/25; N=94; EHP=1650.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x16,normal:18x16,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x26,fast:98x2,medium:108x4,medium:123x5</t>
+          <t>L22 W8/25; N=94; EHP=4419.142007; air:2x4,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x2,medium:83x5,medium:108x4,medium:123x5,normal:17x16,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10018955,10018961,10018957,10048752,10018960,10018955,10018961,10018957,10048752,10018960,10018955,10018961,10018957,10048752,10018960,10018955,10018961,10018958,10018952,10018960,10018955,10018961,10018958,10018952,10018960,10018955,10018961,10018958,10048753,10018963,10018955,10018961,10018959,10048753,10018963,10018955,10018961,10018959,10018953,10018963,10018955,10018961,10018959,10018953,10018963,10018955,10018961,10018962,10018953,10018963,10018955,10018961,10018962,10018954,10018964,10018955,10018961,10018962,10018954,10018964,10018955,10018961,10018964,10018955,10018961,10018964,10018955,10018961,10018964,10018955,10018961,10018955,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018956,10018956,10018956,10018956</t>
+          <t>10018955,10048752,10018957,10048752,10018960,10018955,10048752,10018957,10048752,10018960,10018955,10048752,10018957,10048752,10018960,10018955,10018952,10018958,10018952,10018960,10018955,10018952,10018958,10018952,10018960,10018955,10048753,10018958,10048753,10018963,10018955,10048753,10018959,10048753,10018963,10018955,10018953,10018959,10018953,10018963,10018955,10018953,10018959,10018953,10018963,10018955,10018953,10018962,10018953,10018963,10018955,10018954,10018962,10018954,10018964,10018955,10018954,10018962,10018954,10018964,10018955,10018961,10018964,10018955,10018961,10018964,10018955,10018961,10018964,10018955,10018961,10018955,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018961,10018956,10018956,10018956,10018956,10018956</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L22 W9/25; N=100; EHP=2105.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x16,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L22 W9/25; N=100; EHP=5639.743698; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x17,normal:18x16,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10018968,10018974,10018970,10048754,10018973,10018968,10018974,10018970,10048754,10018973,10018968,10018974,10018970,10018965,10018973,10018968,10018974,10018971,10018965,10018973,10018968,10018974,10018971,10018965,10018973,10018968,10018974,10018971,10048755,10018976,10018968,10018974,10018972,10048755,10018976,10018968,10018974,10018972,10018966,10018976,10018968,10018974,10018972,10018966,10018976,10018968,10018974,10018975,10018966,10018976,10018968,10018974,10018975,10018967,10018977,10018968,10018974,10018975,10018967,10018977,10018968,10018974,10018967,10018977,10018968,10018974,10018977,10018968,10018974,10018977,10018968,10018974,10018968,10018974,10018968,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018969,10018969,10018969,10018969,10018969,10018969,10018969</t>
+          <t>10018968,10048754,10018970,10048754,10018973,10018968,10048754,10018970,10048754,10018973,10018968,10018965,10018970,10018965,10018973,10018968,10018965,10018971,10018965,10018973,10018968,10018965,10018971,10018965,10018973,10018968,10048755,10018971,10048755,10018976,10018968,10048755,10018972,10048755,10018976,10018968,10018966,10018972,10018966,10018976,10018968,10018966,10018972,10018966,10018976,10018968,10018966,10018975,10018966,10018976,10018968,10018967,10018975,10018967,10018977,10018968,10018967,10018975,10018967,10018977,10018968,10018967,10018967,10018977,10018968,10018974,10018977,10018968,10018974,10018977,10018968,10018974,10018968,10018974,10018968,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018974,10018969,10018969,10018969,10018969,10018969,10018969,10018969,10018969</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L22 W10/25; N=106; EHP=3880.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x18,normal:18x19,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x29,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L22 W10/25; N=106; EHP=10398.897058; air:2x4,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x18,normal:18x19,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10018978,10018987,10018980,10048756,10018986,10018981,10018978,10018987,10018980,10048756,10018986,10018981,10018978,10018987,10018980,10048757,10018986,10018982,10018978,10018987,10018983,10048757,10018986,10045222,10018978,10018987,10018983,10048757,10018986,10045223,10018978,10018987,10018983,10048758,10018986,10018985,10018978,10018987,10018984,10048758,10018990,10018985,10018978,10018987,10018984,10048758,10018990,10018988,10018978,10018987,10018984,10048759,10018990,10018988,10018978,10018987,10018989,10048759,10018990,10045224,10018978,10018987,10018989,10048760,10018990,10018992,10018978,10018987,10018989,10048760,10018991,10018978,10018987,10018989,10048760,10018991,10018978,10018987,10018991,10018979,10018987,10018991,10018979,10018987,10018991,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018987,10018987,10018987</t>
+          <t>10018978,10048756,10018980,10048756,10018986,10018981,10018978,10048756,10018980,10048756,10018986,10018981,10018978,10048757,10018980,10048757,10018986,10018982,10018978,10048757,10018983,10048757,10018986,10045222,10018978,10048757,10018983,10048757,10018986,10045223,10018978,10048758,10018983,10048758,10018986,10018985,10018978,10048758,10018984,10048758,10018990,10018985,10018978,10048758,10018984,10048758,10018990,10018988,10018978,10048759,10018984,10048759,10018990,10018988,10018978,10048759,10018989,10048759,10018990,10045224,10018978,10048760,10018989,10048760,10018990,10018992,10018978,10048760,10018989,10048760,10018991,10018978,10048760,10018989,10048760,10018991,10018978,10018987,10018991,10018979,10018987,10018991,10018979,10018987,10018991,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018979,10018987,10018987,10018987,10018987</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L22 W11/25; N=112; EHP=3958.000000; air:2x2,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x14,fast:30x3,heavy:31x2,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x31,heavy:86x2,heavy:88x1,fast:98x4,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L22 W11/25; N=112; EHP=10585.090377; air:2x4,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x6,medium:108x5,medium:123x5,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10018996,10019006,10018998,10048761,10019005,10018999,10018996,10019006,10018998,10048761,10019005,10018999,10018996,10019006,10018998,10048761,10019005,10019000,10018996,10019006,10019001,10018993,10019005,10019000,10018996,10019006,10019001,10018993,10019005,10019003,10018996,10019006,10019001,10048762,10019009,10019004,10018996,10019006,10019001,10048762,10019009,10045225,10018996,10019006,10019002,10048762,10019009,10019007,10018996,10019006,10019002,10018994,10019009,10019007,10018996,10019006,10019002,10018994,10019009,10045226,10018996,10019006,10019002,10018994,10019009,10019011,10018996,10019006,10019008,10018995,10019010,10018996,10019006,10019008,10018995,10019010,10018996,10019006,10019008,10018995,10019010,10018997,10019006,10019010,10018997,10019006,10019010,10018997,10019006,10019010,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10019006,10019006,10019006,10019006</t>
+          <t>10018996,10048761,10018998,10048761,10019005,10018999,10018996,10048761,10018998,10048761,10019005,10018999,10018996,10048761,10018998,10048761,10019005,10019000,10018996,10018993,10019001,10018993,10019005,10019000,10018996,10018993,10019001,10018993,10019005,10019003,10018996,10048762,10019001,10048762,10019009,10019004,10018996,10048762,10019001,10048762,10019009,10045225,10018996,10048762,10019002,10048762,10019009,10019007,10018996,10018994,10019002,10018994,10019009,10019007,10018996,10018994,10019002,10018994,10019009,10045226,10018996,10018994,10019002,10018994,10019009,10019011,10018996,10018995,10019008,10018995,10019010,10018996,10018995,10019008,10018995,10019010,10018996,10018995,10019008,10018995,10019010,10018997,10019006,10019010,10018997,10019006,10019010,10018997,10019006,10019010,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10018997,10019006,10019006,10019006,10019006,10019006</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L22 W12/25; N=118; EHP=4096.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x33,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L22 W12/25; N=118; EHP=10957.784417; air:2x6,air:11x4,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10019015,10019025,10019017,10048763,10019024,10019018,10019015,10019025,10019017,10048763,10019024,10019018,10019015,10019025,10019017,10048763,10019024,10019019,10019015,10019025,10019017,10019012,10019024,10019019,10019015,10019025,10019020,10019012,10019024,10019022,10019015,10019025,10019020,10019012,10019024,10019023,10019015,10019025,10019020,10048764,10019028,10019023,10019015,10019025,10019021,10048764,10019028,10045227,10019015,10019025,10019021,10048764,10019028,10045228,10019015,10019025,10019021,10019013,10019028,10019026,10019015,10019025,10019021,10019013,10019028,10019030,10019015,10019025,10019027,10019013,10019028,10019030,10019015,10019025,10019027,10019014,10019029,10019015,10019025,10019027,10019014,10019029,10019015,10019025,10019014,10019029,10019015,10019025,10019029,10019016,10019025,10019029,10019016,10019025,10019029,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019025,10019025,10019025</t>
+          <t>10019015,10048763,10019017,10048763,10019024,10019018,10019015,10048763,10019017,10048763,10019024,10019018,10019015,10048763,10019017,10048763,10019024,10019019,10019015,10019012,10019017,10019012,10019024,10019019,10019015,10019012,10019020,10019012,10019024,10019022,10019015,10019012,10019020,10019012,10019024,10019023,10019015,10048764,10019020,10048764,10019028,10019023,10019015,10048764,10019021,10048764,10019028,10045227,10019015,10048764,10019021,10048764,10019028,10045228,10019015,10019013,10019021,10019013,10019028,10019026,10019015,10019013,10019021,10019013,10019028,10019030,10019015,10019013,10019027,10019013,10019028,10019030,10019015,10019014,10019027,10019014,10019029,10019015,10019014,10019027,10019014,10019029,10019015,10019014,10019014,10019029,10019015,10019025,10019029,10019016,10019025,10019029,10019016,10019025,10019029,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019016,10019025,10019025,10019025,10019025</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L22 W13/25; N=124; EHP=4996.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x15,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x34,heavy:86x1,heavy:88x1,fast:98x3,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L22 W13/25; N=124; EHP=13367.502734; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x16,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10019034,10019044,10019036,10048765,10019043,10045229,10019034,10019044,10019036,10048765,10019043,10019037,10019034,10019044,10019036,10048765,10019043,10019037,10019034,10019044,10019036,10048765,10019043,10019040,10019034,10019044,10019038,10019031,10019043,10019040,10019034,10019044,10019038,10019031,10019043,10019041,10019034,10019044,10019038,10019031,10019043,10019041,10019034,10019044,10019038,10048766,10019047,10019042,10019034,10019044,10019039,10048766,10019047,10045230,10019034,10019044,10019039,10048766,10019047,10019045,10019034,10019044,10019039,10019032,10019047,10019045,10019034,10019044,10019046,10019032,10019047,10019049,10019034,10019044,10019046,10019032,10019047,10019049,10019034,10019044,10019046,10019033,10019048,10019034,10019044,10019046,10019033,10019048,10019035,10019044,10019033,10019048,10019035,10019044,10019048,10019035,10019044,10019048,10019035,10019044,10019048,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019044,10019044,10019044,10019044,10019044</t>
+          <t>10019034,10048765,10019036,10048765,10019043,10045229,10019034,10048765,10019036,10048765,10019043,10019037,10019034,10048765,10019036,10048765,10019043,10019037,10019034,10048765,10019036,10048765,10019043,10019040,10019034,10019031,10019038,10019031,10019043,10019040,10019034,10019031,10019038,10019031,10019043,10019041,10019034,10019031,10019038,10019031,10019043,10019041,10019034,10048766,10019038,10048766,10019047,10019042,10019034,10048766,10019039,10048766,10019047,10045230,10019034,10048766,10019039,10048766,10019047,10019045,10019034,10019032,10019039,10019032,10019047,10019045,10019034,10019032,10019046,10019032,10019047,10019049,10019034,10019032,10019046,10019032,10019047,10019049,10019034,10019033,10019046,10019033,10019048,10019034,10019033,10019046,10019033,10019048,10019035,10019033,10019033,10019048,10019035,10019044,10019048,10019035,10019044,10019048,10019035,10019044,10019048,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019035,10019044,10019044,10019044,10019044,10019044,10019044</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L22 W14/25; N=130; EHP=6026.000000; air:2x4,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x36,heavy:86x1,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L22 W14/25; N=130; EHP=16126.273197; air:2x8,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x3,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x6,medium:123x6,normal:17x15,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10019053,10019063,10019055,10048767,10019062,10045231,10019058,10019053,10019063,10019055,10048767,10019062,10045232,10019053,10019063,10019055,10048767,10019062,10019059,10019053,10019063,10019055,10019050,10019062,10019059,10019053,10019063,10019056,10019050,10019062,10019060,10019053,10019063,10019056,10019050,10019062,10019060,10019053,10019063,10019056,10048768,10019067,10019061,10019053,10019063,10019056,10048768,10019067,10019061,10019053,10019063,10019057,10048768,10019067,10019064,10019053,10019063,10019057,10019051,10019067,10019065,10019053,10019063,10019057,10019051,10019067,10019065,10019053,10019063,10019057,10019051,10019067,10019069,10019053,10019063,10019066,10019051,10019067,10019069,10019053,10019063,10019066,10019052,10019068,10019053,10019063,10019066,10019052,10019068,10019053,10019063,10019066,10019052,10019068,10019054,10019063,10019068,10019054,10019063,10019068,10019054,10019063,10019068,10019054,10019063,10019068,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019063,10019063,10019063,10019063,10019063,10019063</t>
+          <t>10019053,10048767,10019055,10048767,10019062,10045231,10019058,10019053,10048767,10019055,10048767,10019062,10045232,10019053,10048767,10019055,10048767,10019062,10019059,10019053,10019050,10019055,10019050,10019062,10019059,10019053,10019050,10019056,10019050,10019062,10019060,10019053,10019050,10019056,10019050,10019062,10019060,10019053,10048768,10019056,10048768,10019067,10019061,10019053,10048768,10019056,10048768,10019067,10019061,10019053,10048768,10019057,10048768,10019067,10019064,10019053,10019051,10019057,10019051,10019067,10019065,10019053,10019051,10019057,10019051,10019067,10019065,10019053,10019051,10019057,10019051,10019067,10019069,10019053,10019051,10019066,10019051,10019067,10019069,10019053,10019052,10019066,10019052,10019068,10019053,10019052,10019066,10019052,10019068,10019053,10019052,10019066,10019052,10019068,10019054,10019063,10019068,10019054,10019063,10019068,10019054,10019063,10019068,10019054,10019063,10019068,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019054,10019063,10019063,10019063,10019063,10019063,10019063,10019063</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L22 W15/25; N=136; EHP=10517.000000; air:2x3,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x38,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L22 W15/25; N=136; EHP=28122.794332; air:2x6,air:11x6,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x7,medium:123x7,normal:17x16,normal:18x16,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10019070,10019080,10019072,10048769,10019079,10019073,10019070,10019080,10019072,10048769,10019079,10019073,10019070,10019080,10019072,10048769,10019079,10045233,10019070,10019080,10019072,10048770,10019079,10019076,10019070,10019080,10019074,10048770,10019079,10019076,10019070,10019080,10019074,10048770,10019079,10019077,10019070,10019080,10019074,10048770,10019079,10019077,10019070,10019080,10019074,10048771,10019084,10019078,10019070,10019080,10019074,10048771,10019084,10019078,10019070,10019080,10019075,10048771,10019084,10019081,10019070,10019080,10019075,10048772,10019084,10019081,10019070,10019080,10019075,10048772,10019084,10019082,10019070,10019080,10019075,10048772,10019084,10019082,10019070,10019080,10019083,10048773,10019084,10045234,10019070,10019080,10019083,10048773,10019085,10019070,10019080,10019083,10048773,10019085,10019070,10019080,10019083,10048773,10019085,10019071,10019080,10019085,10019071,10019080,10019085,10019071,10019080,10019085,10019071,10019080,10019085,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019080,10019080,10019080,10019080,10019080</t>
+          <t>10019070,10048769,10019072,10048769,10019079,10019073,10019070,10048769,10019072,10048769,10019079,10019073,10019070,10048769,10019072,10048769,10019079,10045233,10019070,10048770,10019072,10048770,10019079,10019076,10019070,10048770,10019074,10048770,10019079,10019076,10019070,10048770,10019074,10048770,10019079,10019077,10019070,10048770,10019074,10048770,10019079,10019077,10019070,10048771,10019074,10048771,10019084,10019078,10019070,10048771,10019074,10048771,10019084,10019078,10019070,10048771,10019075,10048771,10019084,10019081,10019070,10048772,10019075,10048772,10019084,10019081,10019070,10048772,10019075,10048772,10019084,10019082,10019070,10048772,10019075,10048772,10019084,10019082,10019070,10048773,10019083,10048773,10019084,10045234,10019070,10048773,10019083,10048773,10019085,10019070,10048773,10019083,10048773,10019085,10019070,10048773,10019083,10048773,10019085,10019071,10019080,10019085,10019071,10019080,10019085,10019071,10019080,10019085,10019071,10019080,10019085,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019071,10019080,10019080,10019080,10019080,10019080,10019080</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L22 W16/25; N=142; EHP=10728.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x1,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L22 W16/25; N=142; EHP=28699.734173; air:2x6,air:11x8,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10019089,10019099,10019091,10048774,10019098,10019092,10019089,10019099,10019091,10048774,10019098,10019092,10019089,10019099,10019091,10048774,10019098,10019093,10019089,10019099,10019091,10048774,10019098,10019093,10019089,10019099,10019094,10019086,10019098,10019096,10019089,10019099,10019094,10019086,10019098,10019096,10019089,10019099,10019094,10019086,10019098,10045235,10019089,10019099,10019094,10048775,10019098,10019097,10019089,10019099,10019095,10048775,10019103,10019097,10019089,10019099,10019095,10048775,10019103,10019100,10019089,10019099,10019095,10048775,10019103,10019100,10019089,10019099,10019095,10019087,10019103,10019101,10019089,10019099,10019095,10019087,10019103,10019101,10019089,10019099,10019102,10019087,10019103,10019105,10019089,10019099,10019102,10019088,10019103,10019089,10019099,10019102,10019088,10019104,10019089,10019099,10019102,10019088,10019104,10019089,10019099,10019088,10019104,10019090,10019099,10019104,10019090,10019099,10019104,10019090,10019099,10019104,10019090,10019099,10019104,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019099,10019099,10019099,10019099,10019099</t>
+          <t>10019089,10048774,10019091,10048774,10019098,10019092,10019089,10048774,10019091,10048774,10019098,10019092,10019089,10048774,10019091,10048774,10019098,10019093,10019089,10048774,10019091,10048774,10019098,10019093,10019089,10019086,10019094,10019086,10019098,10019096,10019089,10019086,10019094,10019086,10019098,10019096,10019089,10019086,10019094,10019086,10019098,10045235,10019089,10048775,10019094,10048775,10019098,10019097,10019089,10048775,10019095,10048775,10019103,10019097,10019089,10048775,10019095,10048775,10019103,10019100,10019089,10048775,10019095,10048775,10019103,10019100,10019089,10019087,10019095,10019087,10019103,10019101,10019089,10019087,10019095,10019087,10019103,10019101,10019089,10019087,10019102,10019087,10019103,10019105,10019089,10019088,10019102,10019088,10019103,10019089,10019088,10019102,10019088,10019104,10019089,10019088,10019102,10019088,10019104,10019089,10019088,10019088,10019104,10019090,10019099,10019104,10019090,10019099,10019104,10019090,10019099,10019104,10019090,10019099,10019104,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019090,10019099,10019099,10019099,10019099,10019099,10019099</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L22 W17/25; N=148; EHP=10943.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x8,swarm:84x41,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L22 W17/25; N=148; EHP=29281.958054; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x8,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10019109,10019119,10019111,10048776,10019118,10019112,10019109,10019119,10019111,10048776,10019118,10019112,10019109,10019119,10019111,10048776,10019118,10019113,10019109,10019119,10019111,10048776,10019118,10019113,10019109,10019119,10019111,10019106,10019118,10045236,10019109,10019119,10019114,10019106,10019118,10019116,10019109,10019119,10019114,10019106,10019118,10019116,10019109,10019119,10019114,10048777,10019123,10019117,10019109,10019119,10019114,10048777,10019123,10019117,10019109,10019119,10019115,10048777,10019123,10019120,10019109,10019119,10019115,10048777,10019123,10019120,10019109,10019119,10019115,10019107,10019123,10019121,10019109,10019119,10019115,10019107,10019123,10019121,10019109,10019119,10019122,10019107,10019123,10019125,10019109,10019119,10019122,10019107,10019123,10019125,10019109,10019119,10019122,10019108,10019124,10019109,10019119,10019122,10019108,10019124,10019109,10019119,10019122,10019108,10019124,10019110,10019119,10019124,10019110,10019119,10019124,10019110,10019119,10019124,10019110,10019119,10019124,10019110,10019119,10019124,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019119,10019119,10019119,10019119,10019119,10019119</t>
+          <t>10019109,10048776,10019111,10048776,10019118,10019112,10019109,10048776,10019111,10048776,10019118,10019112,10019109,10048776,10019111,10048776,10019118,10019113,10019109,10048776,10019111,10048776,10019118,10019113,10019109,10019106,10019111,10019106,10019118,10045236,10019109,10019106,10019114,10019106,10019118,10019116,10019109,10019106,10019114,10019106,10019118,10019116,10019109,10048777,10019114,10048777,10019123,10019117,10019109,10048777,10019114,10048777,10019123,10019117,10019109,10048777,10019115,10048777,10019123,10019120,10019109,10048777,10019115,10048777,10019123,10019120,10019109,10019107,10019115,10019107,10019123,10019121,10019109,10019107,10019115,10019107,10019123,10019121,10019109,10019107,10019122,10019107,10019123,10019125,10019109,10019107,10019122,10019107,10019123,10019125,10019109,10019108,10019122,10019108,10019124,10019109,10019108,10019122,10019108,10019124,10019109,10019108,10019122,10019108,10019124,10019110,10019119,10019124,10019110,10019119,10019124,10019110,10019119,10019124,10019110,10019119,10019124,10019110,10019119,10019124,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019110,10019119,10019119,10019119,10019119,10019119,10019119,10019119</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L22 W18/25; N=154; EHP=11690.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x18,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L22 W18/25; N=154; EHP=31264.886243; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x8,normal:17x18,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10019129,10019140,10019131,10048778,10019139,10019132,10019129,10019140,10019131,10048778,10019139,10019132,10019129,10019140,10019131,10048778,10019139,10019133,10019129,10019140,10019131,10048778,10019139,10019133,10019129,10019140,10019134,10019126,10019139,10019136,10019129,10019140,10019134,10019126,10019139,10019136,10019129,10019140,10019134,10019126,10019139,10019137,10019129,10019140,10019134,10019126,10019139,10019137,10019129,10019140,10019134,10048779,10019143,10019138,10019129,10019140,10019135,10048779,10019143,10019138,10019129,10019140,10019135,10048779,10019143,10019141,10019129,10019140,10019135,10019127,10019143,10019141,10019129,10019140,10019135,10019127,10019143,10045237,10019129,10019140,10019135,10019127,10019143,10045237,10019129,10019140,10019142,10019127,10019143,10019145,10019129,10019140,10019142,10019128,10019143,10019145,10019129,10019140,10019142,10019128,10019144,10019129,10019140,10019142,10019128,10019144,10019129,10019140,10019142,10019128,10019144,10019130,10019140,10019144,10019130,10019140,10019144,10019130,10019140,10019144,10019130,10019140,10019144,10019130,10019140,10019144,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019140,10019140,10019140,10019140,10019140,10019140</t>
+          <t>10019129,10048778,10019131,10048778,10019139,10019132,10019129,10048778,10019131,10048778,10019139,10019132,10019129,10048778,10019131,10048778,10019139,10019133,10019129,10048778,10019131,10048778,10019139,10019133,10019129,10019126,10019134,10019126,10019139,10019136,10019129,10019126,10019134,10019126,10019139,10019136,10019129,10019126,10019134,10019126,10019139,10019137,10019129,10019126,10019134,10019126,10019139,10019137,10019129,10048779,10019134,10048779,10019143,10019138,10019129,10048779,10019135,10048779,10019143,10019138,10019129,10048779,10019135,10048779,10019143,10019141,10019129,10019127,10019135,10019127,10019143,10019141,10019129,10019127,10019135,10019127,10019143,10045237,10019129,10019127,10019135,10019127,10019143,10045237,10019129,10019127,10019142,10019127,10019143,10019145,10019129,10019128,10019142,10019128,10019143,10019145,10019129,10019128,10019142,10019128,10019144,10019129,10019128,10019142,10019128,10019144,10019129,10019128,10019142,10019128,10019144,10019130,10019140,10019144,10019130,10019140,10019144,10019130,10019140,10019144,10019130,10019140,10019144,10019130,10019140,10019144,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019130,10019140,10019140,10019140,10019140,10019140,10019140,10019140</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L22 W19/25; N=160; EHP=13541.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L22 W19/25; N=160; EHP=36220.339229; air:2x8,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x4,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10019149,10019160,10019151,10048780,10019159,10019152,10019156,10019149,10019160,10019151,10048780,10019159,10019152,10019149,10019160,10019151,10048780,10019159,10019153,10019149,10019160,10019151,10048780,10019159,10019153,10019149,10019160,10019151,10019146,10019159,10019157,10019149,10019160,10019154,10019146,10019159,10019157,10019149,10019160,10019154,10019146,10019159,10019158,10019149,10019160,10019154,10019146,10019159,10019158,10019149,10019160,10019154,10048781,10019164,10045238,10019149,10019160,10019154,10048781,10019164,10045238,10019149,10019160,10019155,10048781,10019164,10019161,10019149,10019160,10019155,10048781,10019164,10019161,10019149,10019160,10019155,10019147,10019164,10019162,10019149,10019160,10019155,10019147,10019164,10019162,10019149,10019160,10019155,10019147,10019164,10019166,10019149,10019160,10019163,10019147,10019164,10019166,10019149,10019160,10019163,10019148,10019165,10019149,10019160,10019163,10019148,10019165,10019149,10019160,10019163,10019148,10019165,10019149,10019160,10019148,10019165,10019150,10019160,10019165,10019150,10019160,10019165,10019150,10019160,10019165,10019150,10019160,10019165,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019160,10019160,10019160,10019160,10019160,10019160</t>
+          <t>10019149,10048780,10019151,10048780,10019159,10019152,10019156,10019149,10048780,10019151,10048780,10019159,10019152,10019149,10048780,10019151,10048780,10019159,10019153,10019149,10048780,10019151,10048780,10019159,10019153,10019149,10019146,10019151,10019146,10019159,10019157,10019149,10019146,10019154,10019146,10019159,10019157,10019149,10019146,10019154,10019146,10019159,10019158,10019149,10019146,10019154,10019146,10019159,10019158,10019149,10048781,10019154,10048781,10019164,10045238,10019149,10048781,10019154,10048781,10019164,10045238,10019149,10048781,10019155,10048781,10019164,10019161,10019149,10048781,10019155,10048781,10019164,10019161,10019149,10019147,10019155,10019147,10019164,10019162,10019149,10019147,10019155,10019147,10019164,10019162,10019149,10019147,10019155,10019147,10019164,10019166,10019149,10019147,10019163,10019147,10019164,10019166,10019149,10019148,10019163,10019148,10019165,10019149,10019148,10019163,10019148,10019165,10019149,10019148,10019163,10019148,10019165,10019149,10019148,10019148,10019165,10019150,10019160,10019165,10019150,10019160,10019165,10019150,10019160,10019165,10019150,10019160,10019165,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019150,10019160,10019160,10019160,10019160,10019160,10019160,10019160</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L22 W20/25; N=166; EHP=22729.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L22 W20/25; N=166; EHP=60797.984617; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10019170,10019181,10019172,10048782,10019180,10019173,10019170,10019181,10019172,10048782,10019180,10019173,10019170,10019181,10019172,10048782,10019180,10019173,10019170,10019181,10019172,10048782,10019180,10019174,10019170,10019181,10019172,10019167,10019180,10019174,10019170,10019181,10019175,10019167,10019180,10019177,10019170,10019181,10019175,10019167,10019180,10019177,10019170,10019181,10019175,10019167,10019180,10019178,10019170,10019181,10019175,10019167,10019184,10019178,10019170,10019181,10019175,10048783,10019184,10019179,10019170,10019181,10019176,10048783,10019184,10019179,10019170,10019181,10019176,10048783,10019184,10045239,10019170,10019181,10019176,10048783,10019184,10045239,10019170,10019181,10019176,10019168,10019184,10019182,10019170,10019181,10019176,10019168,10019184,10019182,10019170,10019181,10019183,10019168,10019184,10019186,10019170,10019181,10019183,10019168,10019185,10019186,10019170,10019181,10019183,10019169,10019185,10019170,10019181,10019183,10019169,10019185,10019170,10019181,10019183,10019169,10019185,10019170,10019181,10019169,10019185,10019171,10019181,10019185,10019171,10019181,10019185,10019171,10019181,10019185,10019171,10019181,10019185,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019181,10019181,10019181,10019181,10019181,10019181,10019181</t>
+          <t>10019170,10048782,10019172,10048782,10019180,10019173,10019170,10048782,10019172,10048782,10019180,10019173,10019170,10048782,10019172,10048782,10019180,10019173,10019170,10048782,10019172,10048782,10019180,10019174,10019170,10019167,10019172,10019167,10019180,10019174,10019170,10019167,10019175,10019167,10019180,10019177,10019170,10019167,10019175,10019167,10019180,10019177,10019170,10019167,10019175,10019167,10019180,10019178,10019170,10019167,10019175,10019167,10019184,10019178,10019170,10048783,10019175,10048783,10019184,10019179,10019170,10048783,10019176,10048783,10019184,10019179,10019170,10048783,10019176,10048783,10019184,10045239,10019170,10048783,10019176,10048783,10019184,10045239,10019170,10019168,10019176,10019168,10019184,10019182,10019170,10019168,10019176,10019168,10019184,10019182,10019170,10019168,10019183,10019168,10019184,10019186,10019170,10019168,10019183,10019168,10019185,10019186,10019170,10019169,10019183,10019169,10019185,10019170,10019169,10019183,10019169,10019185,10019170,10019169,10019183,10019169,10019185,10019170,10019169,10019169,10019185,10019171,10019181,10019185,10019171,10019181,10019185,10019171,10019181,10019185,10019171,10019181,10019185,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019171,10019181,10019181,10019181,10019181,10019181,10019181,10019181,10019181</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L22 W21/25; N=172; EHP=23184.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x5,heavy:31x3,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x48,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L22 W21/25; N=172; EHP=62038.864048; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x9,normal:17x21,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10019190,10019201,10019192,10048784,10019200,10019193,10019190,10019201,10019192,10048784,10019200,10019193,10019190,10019201,10019192,10048784,10019200,10019194,10019190,10019201,10019192,10048784,10019200,10019194,10019190,10019201,10019192,10019187,10019200,10019194,10019190,10019201,10019192,10019187,10019200,10019197,10019190,10019201,10019195,10019187,10019200,10019197,10019190,10019201,10019195,10019187,10019200,10019198,10019190,10019201,10019195,10048785,10019200,10019198,10019190,10019201,10019195,10048785,10019205,10019199,10019190,10019201,10019195,10048785,10019205,10019199,10019190,10019201,10019196,10048785,10019205,10019202,10019190,10019201,10019196,10019188,10019205,10019202,10019190,10019201,10019196,10019188,10019205,10019203,10019190,10019201,10019196,10019188,10019205,10019203,10019190,10019201,10019196,10019188,10019205,10019207,10019190,10019201,10019204,10019189,10019205,10019207,10019190,10019201,10019204,10019189,10019205,10019190,10019201,10019204,10019189,10019206,10019190,10019201,10019204,10019189,10019206,10019190,10019201,10019204,10019189,10019206,10019190,10019201,10019206,10019191,10019201,10019206,10019191,10019201,10019206,10019191,10019201,10019206,10019191,10019201,10019206,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019201,10019201,10019201,10019201,10019201</t>
+          <t>10019190,10048784,10019192,10048784,10019200,10019193,10019190,10048784,10019192,10048784,10019200,10019193,10019190,10048784,10019192,10048784,10019200,10019194,10019190,10048784,10019192,10048784,10019200,10019194,10019190,10019187,10019192,10019187,10019200,10019194,10019190,10019187,10019192,10019187,10019200,10019197,10019190,10019187,10019195,10019187,10019200,10019197,10019190,10019187,10019195,10019187,10019200,10019198,10019190,10048785,10019195,10048785,10019200,10019198,10019190,10048785,10019195,10048785,10019205,10019199,10019190,10048785,10019195,10048785,10019205,10019199,10019190,10048785,10019196,10048785,10019205,10019202,10019190,10019188,10019196,10019188,10019205,10019202,10019190,10019188,10019196,10019188,10019205,10019203,10019190,10019188,10019196,10019188,10019205,10019203,10019190,10019188,10019196,10019188,10019205,10019207,10019190,10019189,10019204,10019189,10019205,10019207,10019190,10019189,10019204,10019189,10019205,10019190,10019189,10019204,10019189,10019206,10019190,10019189,10019204,10019189,10019206,10019190,10019189,10019204,10019189,10019206,10019190,10019201,10019206,10019191,10019201,10019206,10019191,10019201,10019206,10019191,10019201,10019206,10019191,10019201,10019206,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019191,10019201,10019201,10019201,10019201,10019201,10019201</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L22 W22/25; N=178; EHP=23648.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x22,normal:18x22,fast:30x6,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L22 W22/25; N=178; EHP=63255.811189; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x6,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x8,normal:17x22,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10019211,10019222,10019213,10048786,10019221,10019214,10019211,10019222,10019213,10048786,10019221,10019214,10019211,10019222,10019213,10048786,10019221,10019215,10019211,10019222,10019213,10048786,10019221,10019215,10019211,10019222,10019213,10048786,10019221,10019218,10019211,10019222,10019216,10019208,10019221,10019218,10019211,10019222,10019216,10019208,10019221,10019219,10019211,10019222,10019216,10019208,10019221,10019219,10019211,10019222,10019216,10019208,10019221,10019219,10019211,10019222,10019216,10048787,10019226,10019220,10019211,10019222,10019216,10048787,10019226,10019220,10019211,10019222,10019217,10048787,10019226,10019223,10019211,10019222,10019217,10048787,10019226,10019223,10019211,10019222,10019217,10048787,10019226,10019224,10019211,10019222,10019217,10019209,10019226,10019224,10019211,10019222,10019217,10019209,10019226,10019228,10019211,10019222,10019225,10019209,10019226,10019228,10019211,10019222,10019225,10019209,10019226,10019228,10019211,10019222,10019225,10019210,10019227,10019211,10019222,10019225,10019210,10019227,10019211,10019222,10019225,10019210,10019227,10019211,10019222,10019225,10019210,10019227,10019212,10019222,10019227,10019212,10019222,10019227,10019212,10019222,10019227,10019212,10019222,10019227,10019212,10019222,10019227,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019222,10019222,10019222,10019222,10019222,10019222,10019222</t>
+          <t>10019211,10048786,10019213,10048786,10019221,10019214,10019211,10048786,10019213,10048786,10019221,10019214,10019211,10048786,10019213,10048786,10019221,10019215,10019211,10048786,10019213,10048786,10019221,10019215,10019211,10048786,10019213,10048786,10019221,10019218,10019211,10019208,10019216,10019208,10019221,10019218,10019211,10019208,10019216,10019208,10019221,10019219,10019211,10019208,10019216,10019208,10019221,10019219,10019211,10019208,10019216,10019208,10019221,10019219,10019211,10048787,10019216,10048787,10019226,10019220,10019211,10048787,10019216,10048787,10019226,10019220,10019211,10048787,10019217,10048787,10019226,10019223,10019211,10048787,10019217,10048787,10019226,10019223,10019211,10048787,10019217,10048787,10019226,10019224,10019211,10019209,10019217,10019209,10019226,10019224,10019211,10019209,10019217,10019209,10019226,10019228,10019211,10019209,10019225,10019209,10019226,10019228,10019211,10019209,10019225,10019209,10019226,10019228,10019211,10019210,10019225,10019210,10019227,10019211,10019210,10019225,10019210,10019227,10019211,10019210,10019225,10019210,10019227,10019211,10019210,10019225,10019210,10019227,10019212,10019222,10019227,10019212,10019222,10019227,10019212,10019222,10019227,10019212,10019222,10019227,10019212,10019222,10019227,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019212,10019222,10019222,10019222,10019222,10019222,10019222,10019222,10019222</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L22 W23/25; N=184; EHP=24121.000000; air:2x5,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x51,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x3</t>
+          <t>L22 W23/25; N=184; EHP=64529.746132; air:2x10,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10019232,10019243,10019234,10048788,10019242,10019235,10019232,10019243,10019234,10048788,10019242,10019235,10019232,10019243,10019234,10048788,10019242,10019236,10019232,10019243,10019234,10048788,10019242,10019236,10019232,10019243,10019234,10048788,10019242,10019239,10019232,10019243,10019237,10019229,10019242,10019239,10019232,10019243,10019237,10019229,10019242,10019239,10019232,10019243,10019237,10019229,10019242,10019240,10019232,10019243,10019237,10019229,10019242,10019240,10019232,10019243,10019237,10019229,10019247,10019240,10019232,10019243,10019237,10048789,10019247,10019241,10019232,10019243,10019238,10048789,10019247,10019241,10019232,10019243,10019238,10048789,10019247,10019244,10019232,10019243,10019238,10048789,10019247,10019244,10019232,10019243,10019238,10019230,10019247,10019245,10019232,10019243,10019238,10019230,10019247,10019245,10019232,10019243,10019238,10019230,10019247,10019245,10019232,10019243,10019246,10019230,10019247,10019249,10019232,10019243,10019246,10019230,10019248,10019249,10019232,10019243,10019246,10019231,10019248,10019232,10019243,10019246,10019231,10019248,10019232,10019243,10019246,10019231,10019248,10019233,10019243,10019231,10019248,10019233,10019243,10019248,10019233,10019243,10019248,10019233,10019243,10019248,10019233,10019243,10019248,10019233,10019243,10019248,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019243,10019243,10019243,10019243,10019243,10019243,10019243,10019243</t>
+          <t>10019232,10048788,10019234,10048788,10019242,10019235,10019232,10048788,10019234,10048788,10019242,10019235,10019232,10048788,10019234,10048788,10019242,10019236,10019232,10048788,10019234,10048788,10019242,10019236,10019232,10048788,10019234,10048788,10019242,10019239,10019232,10019229,10019237,10019229,10019242,10019239,10019232,10019229,10019237,10019229,10019242,10019239,10019232,10019229,10019237,10019229,10019242,10019240,10019232,10019229,10019237,10019229,10019242,10019240,10019232,10019229,10019237,10019229,10019247,10019240,10019232,10048789,10019237,10048789,10019247,10019241,10019232,10048789,10019238,10048789,10019247,10019241,10019232,10048789,10019238,10048789,10019247,10019244,10019232,10048789,10019238,10048789,10019247,10019244,10019232,10019230,10019238,10019230,10019247,10019245,10019232,10019230,10019238,10019230,10019247,10019245,10019232,10019230,10019238,10019230,10019247,10019245,10019232,10019230,10019246,10019230,10019247,10019249,10019232,10019230,10019246,10019230,10019248,10019249,10019232,10019231,10019246,10019231,10019248,10019232,10019231,10019246,10019231,10019248,10019232,10019231,10019246,10019231,10019248,10019233,10019231,10019231,10019248,10019233,10019243,10019248,10019233,10019243,10019248,10019233,10019243,10019248,10019233,10019243,10019248,10019233,10019243,10019248,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019233,10019243,10019243,10019243,10019243,10019243,10019243,10019243,10019243,10019243</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L22 W24/25; N=190; EHP=25830.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x23,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x53,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x10,heavy:127x2</t>
+          <t>L22 W24/25; N=190; EHP=69109.864704; air:2x10,air:11x10,air:12x8,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x9,medium:123x10,normal:17x22,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10019253,10019264,10019255,10048790,10019263,10019256,10019271,10019253,10019264,10019255,10048790,10019263,10019256,10019253,10019264,10019255,10048790,10019263,10019257,10019253,10019264,10019255,10048790,10019263,10019257,10019253,10019264,10019255,10019250,10019263,10019260,10019253,10019264,10019255,10019250,10019263,10019260,10019253,10019264,10019258,10019250,10019263,10019260,10019253,10019264,10019258,10019250,10019263,10019261,10019253,10019264,10019258,10019250,10019263,10019261,10019253,10019264,10019258,10048791,10019263,10019262,10019253,10019264,10019258,10048791,10019268,10019262,10019253,10019264,10019259,10048791,10019268,10019262,10019253,10019264,10019259,10048791,10019268,10019265,10019253,10019264,10019259,10048791,10019268,10019265,10019253,10019264,10019259,10019251,10019268,10019266,10019253,10019264,10019259,10019251,10019268,10019266,10019253,10019264,10019259,10019251,10019268,10019266,10019253,10019264,10019267,10019251,10019268,10019270,10019253,10019264,10019267,10019251,10019268,10019270,10019253,10019264,10019267,10019252,10019268,10019253,10019264,10019267,10019252,10019269,10019253,10019264,10019267,10019252,10019269,10019253,10019264,10019267,10019252,10019269,10019254,10019264,10019252,10019269,10019254,10019264,10019269,10019254,10019264,10019269,10019254,10019264,10019269,10019254,10019264,10019269,10019254,10019264,10019269,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019264,10019264,10019264,10019264,10019264,10019264,10019264,10019264</t>
+          <t>10019253,10048790,10019255,10048790,10019263,10019256,10019271,10019253,10048790,10019255,10048790,10019263,10019256,10019253,10048790,10019255,10048790,10019263,10019257,10019253,10048790,10019255,10048790,10019263,10019257,10019253,10019250,10019255,10019250,10019263,10019260,10019253,10019250,10019255,10019250,10019263,10019260,10019253,10019250,10019258,10019250,10019263,10019260,10019253,10019250,10019258,10019250,10019263,10019261,10019253,10019250,10019258,10019250,10019263,10019261,10019253,10048791,10019258,10048791,10019263,10019262,10019253,10048791,10019258,10048791,10019268,10019262,10019253,10048791,10019259,10048791,10019268,10019262,10019253,10048791,10019259,10048791,10019268,10019265,10019253,10048791,10019259,10048791,10019268,10019265,10019253,10019251,10019259,10019251,10019268,10019266,10019253,10019251,10019259,10019251,10019268,10019266,10019253,10019251,10019259,10019251,10019268,10019266,10019253,10019251,10019267,10019251,10019268,10019270,10019253,10019251,10019267,10019251,10019268,10019270,10019253,10019252,10019267,10019252,10019268,10019253,10019252,10019267,10019252,10019269,10019253,10019252,10019267,10019252,10019269,10019253,10019252,10019267,10019252,10019269,10019254,10019252,10019252,10019269,10019254,10019264,10019269,10019254,10019264,10019269,10019254,10019264,10019269,10019254,10019264,10019269,10019254,10019264,10019269,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019254,10019264,10019264,10019264,10019264,10019264,10019264,10019264,10019264,10019264</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L22 W25/25; N=196; EHP=51552.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x23,normal:18x23,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x3,medium:83x10,swarm:84x54,heavy:86x2,heavy:88x3,fast:98x6,medium:108x10,medium:123x9,heavy:127x2,boss:132x1</t>
+          <t>L22 W25/25; N=196; EHP=137922.784872; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x5,fast:64x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x10,medium:108x10,medium:123x9,normal:17x23,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L22/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L22/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>238</v>
+        <v>350</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>231</v>
+        <v>310</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>217</v>
+        <v>360</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>168</v>
+        <v>300</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>161</v>
+        <v>360</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>154</v>
+        <v>290</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>147</v>
+        <v>270</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>133</v>
+        <v>300</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
